--- a/carto_des_risques_Entity_ABC1.xlsx
+++ b/carto_des_risques_Entity_ABC1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ibtihel.ben.khedher\Documents\risk_cartography\risk_cartography\Data_Entries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F2AB86-82FC-4740-8945-6894D7FD5A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46D232EB-7D3E-4578-AFF6-C4591163735B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="956" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
     <sheet name="_calc" sheetId="14" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">All!$A$4:$P$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">All!$A$3:$P$3</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -1369,100 +1369,100 @@
     <t>ABC1</t>
   </si>
   <si>
-    <t>Action 1</t>
-  </si>
-  <si>
-    <t>Action 4</t>
-  </si>
-  <si>
-    <t>Action 3</t>
-  </si>
-  <si>
-    <t>Action 2</t>
-  </si>
-  <si>
-    <t>Action 5</t>
-  </si>
-  <si>
-    <t>Action 6</t>
-  </si>
-  <si>
-    <t>Action 7</t>
-  </si>
-  <si>
-    <t>Action 8</t>
-  </si>
-  <si>
-    <t>Action 9</t>
-  </si>
-  <si>
-    <t>Action 10</t>
-  </si>
-  <si>
-    <t>Action 11</t>
-  </si>
-  <si>
-    <t>Action 12</t>
-  </si>
-  <si>
-    <t>Action 13</t>
-  </si>
-  <si>
-    <t>Action 14</t>
-  </si>
-  <si>
-    <t>Action 15</t>
-  </si>
-  <si>
-    <t>Action 16</t>
-  </si>
-  <si>
-    <t>Action 17</t>
-  </si>
-  <si>
-    <t>Action 18</t>
-  </si>
-  <si>
-    <t>Action 19</t>
-  </si>
-  <si>
-    <t>Action 20</t>
-  </si>
-  <si>
-    <t>Action 21</t>
-  </si>
-  <si>
-    <t>Action 22</t>
-  </si>
-  <si>
-    <t>Action 23</t>
-  </si>
-  <si>
-    <t>Action 24</t>
-  </si>
-  <si>
-    <t>Action 25</t>
-  </si>
-  <si>
-    <t>Action 26</t>
-  </si>
-  <si>
-    <t>Action 27</t>
-  </si>
-  <si>
-    <t>Action 28</t>
-  </si>
-  <si>
-    <t>Action 29</t>
-  </si>
-  <si>
-    <t>Action 30</t>
-  </si>
-  <si>
-    <t>Action 31</t>
-  </si>
-  <si>
-    <t>Action 32</t>
+    <t>Renforcer les audits fournisseurs à risque et formaliser une revue annuelle de conformité achats.</t>
+  </si>
+  <si>
+    <t>Mettre en place un contrôle ex post systématique des prestations intellectuelles sensibles.</t>
+  </si>
+  <si>
+    <t>Déployer un contrôle automatisé du cumul de commandes par fournisseur et abaisser les seuils d’alerte.</t>
+  </si>
+  <si>
+    <t>Créer un registre formalisé des conflits d’intérêts avec déclaration annuelle obligatoire par les acheteurs</t>
+  </si>
+  <si>
+    <t>Renforcer la revue indépendante du fichier fournisseurs et mettre en œuvre des contrôles KYC approfondis.</t>
+  </si>
+  <si>
+    <t>Abaisser les seuils cadeaux &amp; invitations, renforcer les validations hiérarchiques et contrôles a posteriori.</t>
+  </si>
+  <si>
+    <t>Renforcer la due diligence anticorruption des agents commerciaux en zones à risque élevé.</t>
+  </si>
+  <si>
+    <t>Mettre en place une revue conformité dédiée pour les appels d’offres à risque élevé.</t>
+  </si>
+  <si>
+    <t>Soumettre systématiquement les marchés publics à une validation conformité préalable.</t>
+  </si>
+  <si>
+    <t>Mettre en place un reporting périodique des marges et conditions commerciales exceptionnelles.</t>
+  </si>
+  <si>
+    <t>Renforcer les contrôles RH sur les recrutements sensibles et formaliser la traçabilité des décisions.</t>
+  </si>
+  <si>
+    <t>Mettre en place un contrôle annuel des postes sensibles et de la réalité des livrables attendus.</t>
+  </si>
+  <si>
+    <t>Rendre obligatoire la déclaration des liens personnels dans les processus de recrutement.</t>
+  </si>
+  <si>
+    <t>Encadrer strictement les enveloppes de primes et renforcer la revue transverse par la direction et les RH.</t>
+  </si>
+  <si>
+    <t>Renforcer la procédure d’escalade et la traçabilité des demandes de paiements illicites.</t>
+  </si>
+  <si>
+    <t>Mettre en place une revue ciblée et périodique des comptes comptables sensibles.</t>
+  </si>
+  <si>
+    <t>Renforcer les contrôles aléatoires et abaisser les seuils de validation automatique des notes de frais.</t>
+  </si>
+  <si>
+    <t>Renforcer la séparation des tâches et les contrôles bancaires indépendants sur les RIB.</t>
+  </si>
+  <si>
+    <t>Imposer une justification documentaire renforcée pour tous les paiements internationaux.</t>
+  </si>
+  <si>
+    <t>Renforcer la due diligence anticorruption préalable à toute acquisition ou prise de participation.</t>
+  </si>
+  <si>
+    <t>Renforcer les droits de regard, audits et clauses de gouvernance sur les partenaires de JV.</t>
+  </si>
+  <si>
+    <t>Formaliser et documenter les déclarations d’intérêts au niveau du board et des dirigeants.</t>
+  </si>
+  <si>
+    <t>Encadrer strictement les honoraires de conseil et renforcer les comparaisons avec le marché.</t>
+  </si>
+  <si>
+    <t>Renforcer la vérification des bénéficiaires et le suivi effectif de l’utilisation des fonds.</t>
+  </si>
+  <si>
+    <t>Encadrer strictement le sponsoring avec validation conformité et justificatif de contrepartie.</t>
+  </si>
+  <si>
+    <t>Renforcer la sensibilisation des dirigeants aux interdictions légales de financement politique.</t>
+  </si>
+  <si>
+    <t>Mettre en place une double validation systématique et un suivi budgétaire renforcé.</t>
+  </si>
+  <si>
+    <t>Créer un registre de lobbying et formaliser toutes les interactions avec les agents publics.</t>
+  </si>
+  <si>
+    <t>Renforcer la traçabilité et la supervision des échanges avec décideurs publics.</t>
+  </si>
+  <si>
+    <t>Renforcer la supervision managériale des démarches administratives sensibles.</t>
+  </si>
+  <si>
+    <t>Renforcer les validations juridiques et conformité sur les demandes de subventions publiques.</t>
+  </si>
+  <si>
+    <t>Formaliser les contrôles HATVP lors des recrutements sensibles et sensibiliser les managers.</t>
   </si>
 </sst>
 </file>
@@ -21257,7 +21257,7 @@
   <sheetPr>
     <tabColor rgb="FF4558DB"/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -21318,1687 +21318,1687 @@
       <c r="O2" s="63"/>
       <c r="P2" s="63"/>
     </row>
-    <row r="4" spans="1:16" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+    <row r="3" spans="1:16" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="59" t="s">
+      <c r="B3" s="59" t="s">
         <v>220</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C3" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M3" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N3" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="O3" s="8" t="s">
         <v>72</v>
       </c>
     </row>
+    <row r="4" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="22">
+        <v>1</v>
+      </c>
+      <c r="G4" s="22">
+        <v>2</v>
+      </c>
+      <c r="H4" s="23">
+        <f>IF(AND(F4&lt;&gt;"",G4&lt;&gt;""),F4*G4,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I4" s="9" t="str">
+        <f t="shared" ref="I4:I35" si="0">IF(H4="","",IF(H4&gt;=12,"🔴 Critique",IF(H4&gt;=8,"🟠 Élevé",IF(H4&gt;=4,"🟡 Modéré","🟢 Faible"))))</f>
+        <v>🟢 Faible</v>
+      </c>
+      <c r="J4" s="55" t="s">
+        <v>370</v>
+      </c>
+      <c r="K4" s="27">
+        <v>2</v>
+      </c>
+      <c r="L4" s="27">
+        <v>1</v>
+      </c>
+      <c r="M4" s="23">
+        <f t="shared" ref="M4:M35" si="1">IF(AND(K4&lt;&gt;"",L4&lt;&gt;""),K4*L4,"")</f>
+        <v>2</v>
+      </c>
+      <c r="N4" s="9" t="str">
+        <f t="shared" ref="N4:N35" si="2">IF(M4="","",IF(M4&gt;=12,"🔴 Critique",IF(M4&gt;=8,"🟠 Élevé",IF(M4&gt;=4,"🟡 Modéré","🟢 Faible"))))</f>
+        <v>🟢 Faible</v>
+      </c>
+      <c r="O4" s="20" t="s">
+        <v>403</v>
+      </c>
+    </row>
     <row r="5" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="A5" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>76</v>
+      <c r="C5" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>80</v>
       </c>
       <c r="F5" s="22">
         <v>1</v>
       </c>
       <c r="G5" s="22">
-        <v>2</v>
-      </c>
-      <c r="H5" s="23">
-        <f>IF(AND(F5&lt;&gt;"",G5&lt;&gt;""),F5*G5,"")</f>
-        <v>2</v>
-      </c>
-      <c r="I5" s="9" t="str">
-        <f t="shared" ref="I5:I36" si="0">IF(H5="","",IF(H5&gt;=12,"🔴 Critique",IF(H5&gt;=8,"🟠 Élevé",IF(H5&gt;=4,"🟡 Modéré","🟢 Faible"))))</f>
+        <v>4</v>
+      </c>
+      <c r="H5" s="28">
+        <f t="shared" ref="H5:H35" si="3">IF(AND(F5&lt;&gt;"",G5&lt;&gt;""),F5*G5,"")</f>
+        <v>4</v>
+      </c>
+      <c r="I5" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>🟡 Modéré</v>
+      </c>
+      <c r="J5" s="56" t="s">
+        <v>371</v>
+      </c>
+      <c r="K5" s="27">
+        <v>1</v>
+      </c>
+      <c r="L5" s="27">
+        <v>3</v>
+      </c>
+      <c r="M5" s="28">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N5" s="18" t="str">
+        <f t="shared" si="2"/>
         <v>🟢 Faible</v>
       </c>
-      <c r="J5" s="55" t="s">
-        <v>370</v>
-      </c>
-      <c r="K5" s="27">
-        <v>2</v>
-      </c>
-      <c r="L5" s="27">
-        <v>1</v>
-      </c>
-      <c r="M5" s="23">
-        <f t="shared" ref="M5:M36" si="1">IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),K5*L5,"")</f>
-        <v>2</v>
-      </c>
-      <c r="N5" s="9" t="str">
-        <f t="shared" ref="N5:N36" si="2">IF(M5="","",IF(M5&gt;=12,"🔴 Critique",IF(M5&gt;=8,"🟠 Élevé",IF(M5&gt;=4,"🟡 Modéré","🟢 Faible"))))</f>
-        <v>🟢 Faible</v>
-      </c>
       <c r="O5" s="20" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="18" t="s">
+      <c r="A6" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>80</v>
+      <c r="C6" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>84</v>
       </c>
       <c r="F6" s="22">
         <v>1</v>
       </c>
       <c r="G6" s="22">
+        <v>1</v>
+      </c>
+      <c r="H6" s="23">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Faible</v>
+      </c>
+      <c r="J6" s="55" t="s">
+        <v>372</v>
+      </c>
+      <c r="K6" s="27">
+        <v>3</v>
+      </c>
+      <c r="L6" s="27">
         <v>4</v>
       </c>
-      <c r="H6" s="28">
-        <f t="shared" ref="H6:H36" si="3">IF(AND(F6&lt;&gt;"",G6&lt;&gt;""),F6*G6,"")</f>
+      <c r="M6" s="23">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="N6" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>🔴 Critique</v>
+      </c>
+      <c r="O6" s="20" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" s="22">
         <v>4</v>
       </c>
-      <c r="I6" s="18" t="str">
+      <c r="G7" s="22">
+        <v>3</v>
+      </c>
+      <c r="H7" s="28">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="I7" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>🔴 Critique</v>
+      </c>
+      <c r="J7" s="56" t="s">
+        <v>373</v>
+      </c>
+      <c r="K7" s="27">
+        <v>1</v>
+      </c>
+      <c r="L7" s="27">
+        <v>4</v>
+      </c>
+      <c r="M7" s="28">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="N7" s="18" t="str">
+        <f t="shared" si="2"/>
+        <v>🟡 Modéré</v>
+      </c>
+      <c r="O7" s="20" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" s="22">
+        <v>4</v>
+      </c>
+      <c r="G8" s="22">
+        <v>1</v>
+      </c>
+      <c r="H8" s="23">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="I8" s="9" t="str">
         <f t="shared" si="0"/>
         <v>🟡 Modéré</v>
       </c>
-      <c r="J6" s="56" t="s">
-        <v>371</v>
-      </c>
-      <c r="K6" s="27">
+      <c r="J8" s="55" t="s">
+        <v>374</v>
+      </c>
+      <c r="K8" s="27">
+        <v>4</v>
+      </c>
+      <c r="L8" s="27">
         <v>1</v>
       </c>
-      <c r="L6" s="27">
+      <c r="M8" s="23">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="N8" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>🟡 Modéré</v>
+      </c>
+      <c r="O8" s="20" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" s="22">
         <v>3</v>
       </c>
-      <c r="M6" s="28">
+      <c r="G9" s="22">
+        <v>3</v>
+      </c>
+      <c r="H9" s="23">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="I9" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>🟠 Élevé</v>
+      </c>
+      <c r="J9" s="55" t="s">
+        <v>375</v>
+      </c>
+      <c r="K9" s="27">
+        <v>4</v>
+      </c>
+      <c r="L9" s="27">
+        <v>4</v>
+      </c>
+      <c r="M9" s="23">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="N9" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>🔴 Critique</v>
+      </c>
+      <c r="O9" s="20" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" s="22">
+        <v>2</v>
+      </c>
+      <c r="G10" s="22">
+        <v>1</v>
+      </c>
+      <c r="H10" s="28">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="I10" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Faible</v>
+      </c>
+      <c r="J10" s="56" t="s">
+        <v>376</v>
+      </c>
+      <c r="K10" s="27">
+        <v>1</v>
+      </c>
+      <c r="L10" s="27">
+        <v>1</v>
+      </c>
+      <c r="M10" s="28">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N10" s="18" t="str">
+        <f t="shared" si="2"/>
+        <v>🟢 Faible</v>
+      </c>
+      <c r="O10" s="20" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" s="22">
+        <v>3</v>
+      </c>
+      <c r="G11" s="22">
+        <v>3</v>
+      </c>
+      <c r="H11" s="23">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="I11" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>🟠 Élevé</v>
+      </c>
+      <c r="J11" s="55" t="s">
+        <v>377</v>
+      </c>
+      <c r="K11" s="27">
+        <v>3</v>
+      </c>
+      <c r="L11" s="27">
+        <v>4</v>
+      </c>
+      <c r="M11" s="23">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="N11" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>🔴 Critique</v>
+      </c>
+      <c r="O11" s="20" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="F12" s="22">
+        <v>1</v>
+      </c>
+      <c r="G12" s="22">
+        <v>1</v>
+      </c>
+      <c r="H12" s="28">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="I12" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Faible</v>
+      </c>
+      <c r="J12" s="56" t="s">
+        <v>378</v>
+      </c>
+      <c r="K12" s="27">
+        <v>4</v>
+      </c>
+      <c r="L12" s="27">
+        <v>1</v>
+      </c>
+      <c r="M12" s="28">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="N12" s="18" t="str">
+        <f t="shared" si="2"/>
+        <v>🟡 Modéré</v>
+      </c>
+      <c r="O12" s="20" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="F13" s="22">
+        <v>3</v>
+      </c>
+      <c r="G13" s="22">
+        <v>1</v>
+      </c>
+      <c r="H13" s="23">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="I13" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Faible</v>
+      </c>
+      <c r="J13" s="55" t="s">
+        <v>379</v>
+      </c>
+      <c r="K13" s="27">
+        <v>3</v>
+      </c>
+      <c r="L13" s="27">
+        <v>3</v>
+      </c>
+      <c r="M13" s="23">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="N13" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>🟠 Élevé</v>
+      </c>
+      <c r="O13" s="20" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="F14" s="22">
+        <v>3</v>
+      </c>
+      <c r="G14" s="22">
+        <v>2</v>
+      </c>
+      <c r="H14" s="23">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="I14" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>🟡 Modéré</v>
+      </c>
+      <c r="J14" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="K14" s="27">
+        <v>3</v>
+      </c>
+      <c r="L14" s="27">
+        <v>2</v>
+      </c>
+      <c r="M14" s="23">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N14" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>🟡 Modéré</v>
+      </c>
+      <c r="O14" s="20" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="F15" s="22">
+        <v>1</v>
+      </c>
+      <c r="G15" s="22">
+        <v>4</v>
+      </c>
+      <c r="H15" s="28">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="I15" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>🟡 Modéré</v>
+      </c>
+      <c r="J15" s="56" t="s">
+        <v>381</v>
+      </c>
+      <c r="K15" s="27">
+        <v>2</v>
+      </c>
+      <c r="L15" s="27">
+        <v>3</v>
+      </c>
+      <c r="M15" s="28">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N15" s="18" t="str">
+        <f t="shared" si="2"/>
+        <v>🟡 Modéré</v>
+      </c>
+      <c r="O15" s="20" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="F16" s="22">
+        <v>3</v>
+      </c>
+      <c r="G16" s="22">
+        <v>4</v>
+      </c>
+      <c r="H16" s="23">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="I16" s="9" t="str">
+        <f>IF(H16="","",IF(H16&gt;=12,"🔴 Critique",IF(H16&gt;=8,"🟠 Élevé",IF(H16&gt;=4,"🟡 Modéré","🟢 Faible"))))</f>
+        <v>🔴 Critique</v>
+      </c>
+      <c r="J16" s="55" t="s">
+        <v>382</v>
+      </c>
+      <c r="K16" s="27">
+        <v>4</v>
+      </c>
+      <c r="L16" s="27">
+        <v>3</v>
+      </c>
+      <c r="M16" s="23">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="N16" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>🔴 Critique</v>
+      </c>
+      <c r="O16" s="20" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" s="22">
+        <v>2</v>
+      </c>
+      <c r="G17" s="22">
+        <v>3</v>
+      </c>
+      <c r="H17" s="28">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="I17" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>🟡 Modéré</v>
+      </c>
+      <c r="J17" s="56" t="s">
+        <v>383</v>
+      </c>
+      <c r="K17" s="27">
+        <v>4</v>
+      </c>
+      <c r="L17" s="27">
+        <v>4</v>
+      </c>
+      <c r="M17" s="28">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="N17" s="18" t="str">
+        <f t="shared" si="2"/>
+        <v>🔴 Critique</v>
+      </c>
+      <c r="O17" s="20" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="F18" s="22">
+        <v>1</v>
+      </c>
+      <c r="G18" s="22">
+        <v>3</v>
+      </c>
+      <c r="H18" s="23">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="I18" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Faible</v>
+      </c>
+      <c r="J18" s="55" t="s">
+        <v>384</v>
+      </c>
+      <c r="K18" s="27">
+        <v>1</v>
+      </c>
+      <c r="L18" s="27">
+        <v>4</v>
+      </c>
+      <c r="M18" s="23">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="N18" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>🟡 Modéré</v>
+      </c>
+      <c r="O18" s="20" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="F19" s="22">
+        <v>4</v>
+      </c>
+      <c r="G19" s="22">
+        <v>1</v>
+      </c>
+      <c r="H19" s="28">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="I19" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>🟡 Modéré</v>
+      </c>
+      <c r="J19" s="56" t="s">
+        <v>385</v>
+      </c>
+      <c r="K19" s="27">
+        <v>1</v>
+      </c>
+      <c r="L19" s="27">
+        <v>2</v>
+      </c>
+      <c r="M19" s="28">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="N19" s="18" t="str">
+        <f t="shared" si="2"/>
+        <v>🟢 Faible</v>
+      </c>
+      <c r="O19" s="20" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20" s="22">
+        <v>3</v>
+      </c>
+      <c r="G20" s="22">
+        <v>1</v>
+      </c>
+      <c r="H20" s="23">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="I20" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Faible</v>
+      </c>
+      <c r="J20" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="K20" s="27">
+        <v>3</v>
+      </c>
+      <c r="L20" s="27">
+        <v>4</v>
+      </c>
+      <c r="M20" s="23">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="N20" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>🔴 Critique</v>
+      </c>
+      <c r="O20" s="20" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="F21" s="22">
+        <v>2</v>
+      </c>
+      <c r="G21" s="22">
+        <v>1</v>
+      </c>
+      <c r="H21" s="28">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="I21" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Faible</v>
+      </c>
+      <c r="J21" s="56" t="s">
+        <v>387</v>
+      </c>
+      <c r="K21" s="27">
+        <v>3</v>
+      </c>
+      <c r="L21" s="27">
+        <v>3</v>
+      </c>
+      <c r="M21" s="28">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="N21" s="18" t="str">
+        <f t="shared" si="2"/>
+        <v>🟠 Élevé</v>
+      </c>
+      <c r="O21" s="20" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="F22" s="22">
+        <v>2</v>
+      </c>
+      <c r="G22" s="22">
+        <v>1</v>
+      </c>
+      <c r="H22" s="23">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="I22" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢 Faible</v>
+      </c>
+      <c r="J22" s="55" t="s">
+        <v>388</v>
+      </c>
+      <c r="K22" s="27">
+        <v>3</v>
+      </c>
+      <c r="L22" s="27">
+        <v>1</v>
+      </c>
+      <c r="M22" s="23">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="N6" s="18" t="str">
+      <c r="N22" s="9" t="str">
         <f t="shared" si="2"/>
         <v>🟢 Faible</v>
       </c>
-      <c r="O6" s="25" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="F7" s="22">
+      <c r="O22" s="20" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="F23" s="22">
+        <v>4</v>
+      </c>
+      <c r="G23" s="22">
+        <v>3</v>
+      </c>
+      <c r="H23" s="23">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="I23" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>🔴 Critique</v>
+      </c>
+      <c r="J23" s="55" t="s">
+        <v>389</v>
+      </c>
+      <c r="K23" s="27">
+        <v>3</v>
+      </c>
+      <c r="L23" s="27">
+        <v>3</v>
+      </c>
+      <c r="M23" s="23">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="N23" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>🟠 Élevé</v>
+      </c>
+      <c r="O23" s="20" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F24" s="22">
+        <v>3</v>
+      </c>
+      <c r="G24" s="22">
+        <v>3</v>
+      </c>
+      <c r="H24" s="28">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="I24" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>🟠 Élevé</v>
+      </c>
+      <c r="J24" s="56" t="s">
+        <v>390</v>
+      </c>
+      <c r="K24" s="27">
+        <v>4</v>
+      </c>
+      <c r="L24" s="27">
         <v>1</v>
       </c>
-      <c r="G7" s="22">
+      <c r="M24" s="28">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="N24" s="18" t="str">
+        <f t="shared" si="2"/>
+        <v>🟡 Modéré</v>
+      </c>
+      <c r="O24" s="20" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="F25" s="22">
+        <v>4</v>
+      </c>
+      <c r="G25" s="22">
         <v>1</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H25" s="23">
         <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="I25" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>🟡 Modéré</v>
+      </c>
+      <c r="J25" s="55" t="s">
+        <v>391</v>
+      </c>
+      <c r="K25" s="27">
+        <v>2</v>
+      </c>
+      <c r="L25" s="27">
+        <v>3</v>
+      </c>
+      <c r="M25" s="23">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N25" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>🟡 Modéré</v>
+      </c>
+      <c r="O25" s="20" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="F26" s="22">
+        <v>3</v>
+      </c>
+      <c r="G26" s="22">
+        <v>2</v>
+      </c>
+      <c r="H26" s="28">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="I26" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>🟡 Modéré</v>
+      </c>
+      <c r="J26" s="56" t="s">
+        <v>392</v>
+      </c>
+      <c r="K26" s="27">
         <v>1</v>
       </c>
-      <c r="I7" s="9" t="str">
+      <c r="L26" s="27">
+        <v>2</v>
+      </c>
+      <c r="M26" s="28">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="N26" s="18" t="str">
+        <f t="shared" si="2"/>
+        <v>🟢 Faible</v>
+      </c>
+      <c r="O26" s="20" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="F27" s="22">
+        <v>2</v>
+      </c>
+      <c r="G27" s="22">
+        <v>2</v>
+      </c>
+      <c r="H27" s="23">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="I27" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>🟡 Modéré</v>
+      </c>
+      <c r="J27" s="55" t="s">
+        <v>393</v>
+      </c>
+      <c r="K27" s="27">
+        <v>2</v>
+      </c>
+      <c r="L27" s="27">
+        <v>4</v>
+      </c>
+      <c r="M27" s="23">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="N27" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>🟠 Élevé</v>
+      </c>
+      <c r="O27" s="20" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="F28" s="22">
+        <v>4</v>
+      </c>
+      <c r="G28" s="22">
+        <v>2</v>
+      </c>
+      <c r="H28" s="28">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="I28" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>🟠 Élevé</v>
+      </c>
+      <c r="J28" s="56" t="s">
+        <v>394</v>
+      </c>
+      <c r="K28" s="27">
+        <v>4</v>
+      </c>
+      <c r="L28" s="27">
+        <v>2</v>
+      </c>
+      <c r="M28" s="28">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="N28" s="18" t="str">
+        <f t="shared" si="2"/>
+        <v>🟠 Élevé</v>
+      </c>
+      <c r="O28" s="20" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="F29" s="22">
+        <v>4</v>
+      </c>
+      <c r="G29" s="22">
+        <v>2</v>
+      </c>
+      <c r="H29" s="23">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="I29" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>🟠 Élevé</v>
+      </c>
+      <c r="J29" s="55" t="s">
+        <v>395</v>
+      </c>
+      <c r="K29" s="27">
+        <v>3</v>
+      </c>
+      <c r="L29" s="27">
+        <v>3</v>
+      </c>
+      <c r="M29" s="23">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="N29" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>🟠 Élevé</v>
+      </c>
+      <c r="O29" s="20" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="F30" s="22">
+        <v>3</v>
+      </c>
+      <c r="G30" s="22">
+        <v>3</v>
+      </c>
+      <c r="H30" s="28">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="I30" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>🟠 Élevé</v>
+      </c>
+      <c r="J30" s="56" t="s">
+        <v>396</v>
+      </c>
+      <c r="K30" s="27">
+        <v>3</v>
+      </c>
+      <c r="L30" s="27">
+        <v>1</v>
+      </c>
+      <c r="M30" s="28">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N30" s="18" t="str">
+        <f t="shared" si="2"/>
+        <v>🟢 Faible</v>
+      </c>
+      <c r="O30" s="20" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="F31" s="22">
+        <v>4</v>
+      </c>
+      <c r="G31" s="22">
+        <v>4</v>
+      </c>
+      <c r="H31" s="23">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="I31" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>🔴 Critique</v>
+      </c>
+      <c r="J31" s="55" t="s">
+        <v>397</v>
+      </c>
+      <c r="K31" s="27">
+        <v>4</v>
+      </c>
+      <c r="L31" s="27">
+        <v>4</v>
+      </c>
+      <c r="M31" s="23">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="N31" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>🔴 Critique</v>
+      </c>
+      <c r="O31" s="20" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="E32" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="F32" s="22">
+        <v>3</v>
+      </c>
+      <c r="G32" s="22">
+        <v>2</v>
+      </c>
+      <c r="H32" s="28">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="I32" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>🟡 Modéré</v>
+      </c>
+      <c r="J32" s="56" t="s">
+        <v>398</v>
+      </c>
+      <c r="K32" s="27">
+        <v>3</v>
+      </c>
+      <c r="L32" s="27">
+        <v>1</v>
+      </c>
+      <c r="M32" s="28">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N32" s="18" t="str">
+        <f t="shared" si="2"/>
+        <v>🟢 Faible</v>
+      </c>
+      <c r="O32" s="20" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="F33" s="22">
+        <v>1</v>
+      </c>
+      <c r="G33" s="22">
+        <v>3</v>
+      </c>
+      <c r="H33" s="23">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="I33" s="9" t="str">
         <f t="shared" si="0"/>
         <v>🟢 Faible</v>
       </c>
-      <c r="J7" s="55" t="s">
-        <v>372</v>
-      </c>
-      <c r="K7" s="27">
+      <c r="J33" s="55" t="s">
+        <v>399</v>
+      </c>
+      <c r="K33" s="27">
         <v>3</v>
       </c>
-      <c r="L7" s="27">
+      <c r="L33" s="27">
+        <v>2</v>
+      </c>
+      <c r="M33" s="23">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N33" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>🟡 Modéré</v>
+      </c>
+      <c r="O33" s="20" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="E34" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="F34" s="22">
         <v>4</v>
       </c>
-      <c r="M7" s="23">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="N7" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>🔴 Critique</v>
-      </c>
-      <c r="O7" s="25" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F8" s="22">
+      <c r="G34" s="22">
+        <v>2</v>
+      </c>
+      <c r="H34" s="28">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="I34" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>🟠 Élevé</v>
+      </c>
+      <c r="J34" s="56" t="s">
+        <v>400</v>
+      </c>
+      <c r="K34" s="27">
+        <v>1</v>
+      </c>
+      <c r="L34" s="27">
         <v>4</v>
       </c>
-      <c r="G8" s="22">
-        <v>3</v>
-      </c>
-      <c r="H8" s="28">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="I8" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>🔴 Critique</v>
-      </c>
-      <c r="J8" s="56" t="s">
-        <v>373</v>
-      </c>
-      <c r="K8" s="27">
-        <v>1</v>
-      </c>
-      <c r="L8" s="27">
-        <v>4</v>
-      </c>
-      <c r="M8" s="28">
+      <c r="M34" s="28">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="N8" s="18" t="str">
+      <c r="N34" s="18" t="str">
         <f t="shared" si="2"/>
         <v>🟡 Modéré</v>
       </c>
-      <c r="O8" s="25" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="F9" s="22">
-        <v>4</v>
-      </c>
-      <c r="G9" s="22">
+      <c r="O34" s="20" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="F35" s="22">
         <v>1</v>
       </c>
-      <c r="H9" s="23">
+      <c r="G35" s="22">
+        <v>3</v>
+      </c>
+      <c r="H35" s="23">
         <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="I9" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>🟡 Modéré</v>
-      </c>
-      <c r="J9" s="55" t="s">
-        <v>374</v>
-      </c>
-      <c r="K9" s="27">
-        <v>4</v>
-      </c>
-      <c r="L9" s="27">
-        <v>1</v>
-      </c>
-      <c r="M9" s="23">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="N9" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>🟡 Modéré</v>
-      </c>
-      <c r="O9" s="25" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="F10" s="22">
         <v>3</v>
       </c>
-      <c r="G10" s="22">
-        <v>3</v>
-      </c>
-      <c r="H10" s="23">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
-      <c r="I10" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>🟠 Élevé</v>
-      </c>
-      <c r="J10" s="55" t="s">
-        <v>375</v>
-      </c>
-      <c r="K10" s="27">
-        <v>4</v>
-      </c>
-      <c r="L10" s="27">
-        <v>4</v>
-      </c>
-      <c r="M10" s="23">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="N10" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>🔴 Critique</v>
-      </c>
-      <c r="O10" s="25" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="F11" s="22">
-        <v>2</v>
-      </c>
-      <c r="G11" s="22">
-        <v>1</v>
-      </c>
-      <c r="H11" s="28">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="I11" s="18" t="str">
+      <c r="I35" s="9" t="str">
         <f t="shared" si="0"/>
         <v>🟢 Faible</v>
       </c>
-      <c r="J11" s="56" t="s">
-        <v>376</v>
-      </c>
-      <c r="K11" s="27">
-        <v>1</v>
-      </c>
-      <c r="L11" s="27">
-        <v>1</v>
-      </c>
-      <c r="M11" s="28">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N11" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v>🟢 Faible</v>
-      </c>
-      <c r="O11" s="25" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="F12" s="22">
+      <c r="J35" s="55" t="s">
+        <v>401</v>
+      </c>
+      <c r="K35" s="27">
         <v>3</v>
       </c>
-      <c r="G12" s="22">
+      <c r="L35" s="27">
         <v>3</v>
       </c>
-      <c r="H12" s="23">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
-      <c r="I12" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>🟠 Élevé</v>
-      </c>
-      <c r="J12" s="55" t="s">
-        <v>377</v>
-      </c>
-      <c r="K12" s="27">
-        <v>3</v>
-      </c>
-      <c r="L12" s="27">
-        <v>4</v>
-      </c>
-      <c r="M12" s="23">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="N12" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>🔴 Critique</v>
-      </c>
-      <c r="O12" s="25" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="F13" s="22">
-        <v>1</v>
-      </c>
-      <c r="G13" s="22">
-        <v>1</v>
-      </c>
-      <c r="H13" s="28">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="I13" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>🟢 Faible</v>
-      </c>
-      <c r="J13" s="56" t="s">
-        <v>378</v>
-      </c>
-      <c r="K13" s="27">
-        <v>4</v>
-      </c>
-      <c r="L13" s="27">
-        <v>1</v>
-      </c>
-      <c r="M13" s="28">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="N13" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v>🟡 Modéré</v>
-      </c>
-      <c r="O13" s="25" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="F14" s="22">
-        <v>3</v>
-      </c>
-      <c r="G14" s="22">
-        <v>1</v>
-      </c>
-      <c r="H14" s="23">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="I14" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>🟢 Faible</v>
-      </c>
-      <c r="J14" s="55" t="s">
-        <v>379</v>
-      </c>
-      <c r="K14" s="27">
-        <v>3</v>
-      </c>
-      <c r="L14" s="27">
-        <v>3</v>
-      </c>
-      <c r="M14" s="23">
+      <c r="M35" s="23">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="N14" s="9" t="str">
+      <c r="N35" s="9" t="str">
         <f t="shared" si="2"/>
         <v>🟠 Élevé</v>
       </c>
-      <c r="O14" s="25" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="F15" s="22">
-        <v>3</v>
-      </c>
-      <c r="G15" s="22">
-        <v>2</v>
-      </c>
-      <c r="H15" s="23">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="I15" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>🟡 Modéré</v>
-      </c>
-      <c r="J15" s="55" t="s">
-        <v>380</v>
-      </c>
-      <c r="K15" s="27">
-        <v>3</v>
-      </c>
-      <c r="L15" s="27">
-        <v>2</v>
-      </c>
-      <c r="M15" s="23">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="N15" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>🟡 Modéré</v>
-      </c>
-      <c r="O15" s="25" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="F16" s="22">
-        <v>1</v>
-      </c>
-      <c r="G16" s="22">
-        <v>4</v>
-      </c>
-      <c r="H16" s="28">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="I16" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>🟡 Modéré</v>
-      </c>
-      <c r="J16" s="56" t="s">
-        <v>381</v>
-      </c>
-      <c r="K16" s="27">
-        <v>2</v>
-      </c>
-      <c r="L16" s="27">
-        <v>3</v>
-      </c>
-      <c r="M16" s="28">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="N16" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v>🟡 Modéré</v>
-      </c>
-      <c r="O16" s="25" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="F17" s="22">
-        <v>3</v>
-      </c>
-      <c r="G17" s="22">
-        <v>4</v>
-      </c>
-      <c r="H17" s="23">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="I17" s="9" t="str">
-        <f>IF(H17="","",IF(H17&gt;=12,"🔴 Critique",IF(H17&gt;=8,"🟠 Élevé",IF(H17&gt;=4,"🟡 Modéré","🟢 Faible"))))</f>
-        <v>🔴 Critique</v>
-      </c>
-      <c r="J17" s="55" t="s">
-        <v>382</v>
-      </c>
-      <c r="K17" s="27">
-        <v>4</v>
-      </c>
-      <c r="L17" s="27">
-        <v>3</v>
-      </c>
-      <c r="M17" s="23">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="N17" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>🔴 Critique</v>
-      </c>
-      <c r="O17" s="25" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="F18" s="22">
-        <v>2</v>
-      </c>
-      <c r="G18" s="22">
-        <v>3</v>
-      </c>
-      <c r="H18" s="28">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="I18" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>🟡 Modéré</v>
-      </c>
-      <c r="J18" s="56" t="s">
-        <v>383</v>
-      </c>
-      <c r="K18" s="27">
-        <v>4</v>
-      </c>
-      <c r="L18" s="27">
-        <v>4</v>
-      </c>
-      <c r="M18" s="28">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="N18" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v>🔴 Critique</v>
-      </c>
-      <c r="O18" s="25" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="E19" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="F19" s="22">
-        <v>1</v>
-      </c>
-      <c r="G19" s="22">
-        <v>3</v>
-      </c>
-      <c r="H19" s="23">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="I19" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>🟢 Faible</v>
-      </c>
-      <c r="J19" s="55" t="s">
-        <v>384</v>
-      </c>
-      <c r="K19" s="27">
-        <v>1</v>
-      </c>
-      <c r="L19" s="27">
-        <v>4</v>
-      </c>
-      <c r="M19" s="23">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="N19" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>🟡 Modéré</v>
-      </c>
-      <c r="O19" s="25" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="F20" s="22">
-        <v>4</v>
-      </c>
-      <c r="G20" s="22">
-        <v>1</v>
-      </c>
-      <c r="H20" s="28">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="I20" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>🟡 Modéré</v>
-      </c>
-      <c r="J20" s="56" t="s">
-        <v>385</v>
-      </c>
-      <c r="K20" s="27">
-        <v>1</v>
-      </c>
-      <c r="L20" s="27">
-        <v>2</v>
-      </c>
-      <c r="M20" s="28">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="N20" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v>🟢 Faible</v>
-      </c>
-      <c r="O20" s="25" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="E21" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="F21" s="22">
-        <v>3</v>
-      </c>
-      <c r="G21" s="22">
-        <v>1</v>
-      </c>
-      <c r="H21" s="23">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="I21" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>🟢 Faible</v>
-      </c>
-      <c r="J21" s="55" t="s">
-        <v>386</v>
-      </c>
-      <c r="K21" s="27">
-        <v>3</v>
-      </c>
-      <c r="L21" s="27">
-        <v>4</v>
-      </c>
-      <c r="M21" s="23">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="N21" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>🔴 Critique</v>
-      </c>
-      <c r="O21" s="25" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="F22" s="22">
-        <v>2</v>
-      </c>
-      <c r="G22" s="22">
-        <v>1</v>
-      </c>
-      <c r="H22" s="28">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="I22" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>🟢 Faible</v>
-      </c>
-      <c r="J22" s="56" t="s">
-        <v>387</v>
-      </c>
-      <c r="K22" s="27">
-        <v>3</v>
-      </c>
-      <c r="L22" s="27">
-        <v>3</v>
-      </c>
-      <c r="M22" s="28">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="N22" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v>🟠 Élevé</v>
-      </c>
-      <c r="O22" s="25" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="F23" s="22">
-        <v>2</v>
-      </c>
-      <c r="G23" s="22">
-        <v>1</v>
-      </c>
-      <c r="H23" s="23">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="I23" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>🟢 Faible</v>
-      </c>
-      <c r="J23" s="55" t="s">
-        <v>388</v>
-      </c>
-      <c r="K23" s="27">
-        <v>3</v>
-      </c>
-      <c r="L23" s="27">
-        <v>1</v>
-      </c>
-      <c r="M23" s="23">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="N23" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>🟢 Faible</v>
-      </c>
-      <c r="O23" s="25" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="E24" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="F24" s="22">
-        <v>4</v>
-      </c>
-      <c r="G24" s="22">
-        <v>3</v>
-      </c>
-      <c r="H24" s="23">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="I24" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>🔴 Critique</v>
-      </c>
-      <c r="J24" s="55" t="s">
-        <v>389</v>
-      </c>
-      <c r="K24" s="27">
-        <v>3</v>
-      </c>
-      <c r="L24" s="27">
-        <v>3</v>
-      </c>
-      <c r="M24" s="23">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="N24" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>🟠 Élevé</v>
-      </c>
-      <c r="O24" s="25" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="F25" s="22">
-        <v>3</v>
-      </c>
-      <c r="G25" s="22">
-        <v>3</v>
-      </c>
-      <c r="H25" s="28">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
-      <c r="I25" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>🟠 Élevé</v>
-      </c>
-      <c r="J25" s="56" t="s">
-        <v>390</v>
-      </c>
-      <c r="K25" s="27">
-        <v>4</v>
-      </c>
-      <c r="L25" s="27">
-        <v>1</v>
-      </c>
-      <c r="M25" s="28">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="N25" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v>🟡 Modéré</v>
-      </c>
-      <c r="O25" s="25" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="E26" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="F26" s="22">
-        <v>4</v>
-      </c>
-      <c r="G26" s="22">
-        <v>1</v>
-      </c>
-      <c r="H26" s="23">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="I26" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>🟡 Modéré</v>
-      </c>
-      <c r="J26" s="55" t="s">
-        <v>391</v>
-      </c>
-      <c r="K26" s="27">
-        <v>2</v>
-      </c>
-      <c r="L26" s="27">
-        <v>3</v>
-      </c>
-      <c r="M26" s="23">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="N26" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>🟡 Modéré</v>
-      </c>
-      <c r="O26" s="25" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="C27" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="F27" s="22">
-        <v>3</v>
-      </c>
-      <c r="G27" s="22">
-        <v>2</v>
-      </c>
-      <c r="H27" s="28">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="I27" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>🟡 Modéré</v>
-      </c>
-      <c r="J27" s="56" t="s">
-        <v>392</v>
-      </c>
-      <c r="K27" s="27">
-        <v>1</v>
-      </c>
-      <c r="L27" s="27">
-        <v>2</v>
-      </c>
-      <c r="M27" s="28">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="N27" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v>🟢 Faible</v>
-      </c>
-      <c r="O27" s="25" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="E28" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="F28" s="22">
-        <v>2</v>
-      </c>
-      <c r="G28" s="22">
-        <v>2</v>
-      </c>
-      <c r="H28" s="23">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="I28" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>🟡 Modéré</v>
-      </c>
-      <c r="J28" s="55" t="s">
-        <v>393</v>
-      </c>
-      <c r="K28" s="27">
-        <v>2</v>
-      </c>
-      <c r="L28" s="27">
-        <v>4</v>
-      </c>
-      <c r="M28" s="23">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="N28" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>🟠 Élevé</v>
-      </c>
-      <c r="O28" s="25" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="E29" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="F29" s="22">
-        <v>4</v>
-      </c>
-      <c r="G29" s="22">
-        <v>2</v>
-      </c>
-      <c r="H29" s="28">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="I29" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>🟠 Élevé</v>
-      </c>
-      <c r="J29" s="56" t="s">
-        <v>394</v>
-      </c>
-      <c r="K29" s="27">
-        <v>4</v>
-      </c>
-      <c r="L29" s="27">
-        <v>2</v>
-      </c>
-      <c r="M29" s="28">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="N29" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v>🟠 Élevé</v>
-      </c>
-      <c r="O29" s="25" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="E30" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="F30" s="22">
-        <v>4</v>
-      </c>
-      <c r="G30" s="22">
-        <v>2</v>
-      </c>
-      <c r="H30" s="23">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="I30" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>🟠 Élevé</v>
-      </c>
-      <c r="J30" s="55" t="s">
-        <v>395</v>
-      </c>
-      <c r="K30" s="27">
-        <v>3</v>
-      </c>
-      <c r="L30" s="27">
-        <v>3</v>
-      </c>
-      <c r="M30" s="23">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="N30" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>🟠 Élevé</v>
-      </c>
-      <c r="O30" s="25" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="D31" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="E31" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="F31" s="22">
-        <v>3</v>
-      </c>
-      <c r="G31" s="22">
-        <v>3</v>
-      </c>
-      <c r="H31" s="28">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
-      <c r="I31" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>🟠 Élevé</v>
-      </c>
-      <c r="J31" s="56" t="s">
-        <v>396</v>
-      </c>
-      <c r="K31" s="27">
-        <v>3</v>
-      </c>
-      <c r="L31" s="27">
-        <v>1</v>
-      </c>
-      <c r="M31" s="28">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="N31" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v>🟢 Faible</v>
-      </c>
-      <c r="O31" s="25" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="E32" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="F32" s="22">
-        <v>4</v>
-      </c>
-      <c r="G32" s="22">
-        <v>4</v>
-      </c>
-      <c r="H32" s="23">
-        <f t="shared" si="3"/>
-        <v>16</v>
-      </c>
-      <c r="I32" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>🔴 Critique</v>
-      </c>
-      <c r="J32" s="55" t="s">
-        <v>397</v>
-      </c>
-      <c r="K32" s="27">
-        <v>4</v>
-      </c>
-      <c r="L32" s="27">
-        <v>4</v>
-      </c>
-      <c r="M32" s="23">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="N32" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>🔴 Critique</v>
-      </c>
-      <c r="O32" s="25" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="C33" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="E33" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="F33" s="22">
-        <v>3</v>
-      </c>
-      <c r="G33" s="22">
-        <v>2</v>
-      </c>
-      <c r="H33" s="28">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="I33" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>🟡 Modéré</v>
-      </c>
-      <c r="J33" s="56" t="s">
-        <v>398</v>
-      </c>
-      <c r="K33" s="27">
-        <v>3</v>
-      </c>
-      <c r="L33" s="27">
-        <v>1</v>
-      </c>
-      <c r="M33" s="28">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="N33" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v>🟢 Faible</v>
-      </c>
-      <c r="O33" s="25" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="C34" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="E34" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="F34" s="22">
-        <v>1</v>
-      </c>
-      <c r="G34" s="22">
-        <v>3</v>
-      </c>
-      <c r="H34" s="23">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="I34" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>🟢 Faible</v>
-      </c>
-      <c r="J34" s="55" t="s">
-        <v>399</v>
-      </c>
-      <c r="K34" s="27">
-        <v>3</v>
-      </c>
-      <c r="L34" s="27">
-        <v>2</v>
-      </c>
-      <c r="M34" s="23">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="N34" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>🟡 Modéré</v>
-      </c>
-      <c r="O34" s="25" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="C35" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="D35" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="E35" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="F35" s="22">
-        <v>4</v>
-      </c>
-      <c r="G35" s="22">
-        <v>2</v>
-      </c>
-      <c r="H35" s="28">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="I35" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>🟠 Élevé</v>
-      </c>
-      <c r="J35" s="56" t="s">
-        <v>400</v>
-      </c>
-      <c r="K35" s="27">
-        <v>1</v>
-      </c>
-      <c r="L35" s="27">
-        <v>4</v>
-      </c>
-      <c r="M35" s="28">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="N35" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v>🟡 Modéré</v>
-      </c>
-      <c r="O35" s="25" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="E36" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="F36" s="22">
-        <v>1</v>
-      </c>
-      <c r="G36" s="22">
-        <v>3</v>
-      </c>
-      <c r="H36" s="23">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="I36" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>🟢 Faible</v>
-      </c>
-      <c r="J36" s="55" t="s">
-        <v>401</v>
-      </c>
-      <c r="K36" s="27">
-        <v>3</v>
-      </c>
-      <c r="L36" s="27">
-        <v>3</v>
-      </c>
-      <c r="M36" s="23">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="N36" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>🟠 Élevé</v>
-      </c>
-      <c r="O36" s="25" t="s">
+      <c r="O35" s="20" t="s">
         <v>434</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P4" xr:uid="{953F9F15-A9A3-439B-B271-23848B18BCFD}"/>
+  <autoFilter ref="A3:P3" xr:uid="{953F9F15-A9A3-439B-B271-23848B18BCFD}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
